--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488040_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488040_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3579</v>
+        <v>3.5959</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6318</v>
+        <v>3.898</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.274</v>
+        <v>-0.302</v>
       </c>
       <c r="G2" t="n">
         <v>1.1423</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1978</v>
+        <v>0.4358</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5064</v>
+        <v>-0.2403</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7042</v>
+        <v>0.6761</v>
       </c>
       <c r="V2" t="n">
         <v>2.4142</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0159</v>
+        <v>0.2259</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2488</v>
+        <v>-1.9827</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2648</v>
+        <v>2.2086</v>
       </c>
       <c r="G4" t="n">
         <v>-1.318</v>
@@ -766,13 +766,13 @@
         <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0653</v>
+        <v>0.2753</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.312</v>
+        <v>-0.0459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3773</v>
+        <v>0.3211</v>
       </c>
       <c r="V4" t="n">
         <v>0.674</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>S. OKUNGHAE FRANCIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.201</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4662</v>
+        <v>-0.3445</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2652</v>
+        <v>0.257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0606</v>
+        <v>-1.2016</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8258</v>
+        <v>-0.8514</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7652</v>
+        <v>-0.3502</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1825</v>
+        <v>-0.2758</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2914</v>
+        <v>-0.3159</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1089</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1219</v>
+        <v>-0.9258</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4656</v>
+        <v>-0.5355</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6563</v>
+        <v>-0.3904</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1176</v>
+        <v>-0.0688</v>
       </c>
       <c r="U5" t="n">
-        <v>0.396</v>
+        <v>0.1918</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. OKUNGHAE FRANCIS</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7144</v>
+        <v>-0.2061</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7749</v>
+        <v>-0.4433</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0605</v>
+        <v>0.2371</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2016</v>
+        <v>0.0606</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8514</v>
+        <v>0.8258</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3502</v>
+        <v>-0.7652</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2758</v>
+        <v>1.1825</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3159</v>
+        <v>1.2914</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>-0.1089</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9258</v>
+        <v>-1.1219</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5355</v>
+        <v>-0.4656</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3904</v>
+        <v>-0.6563</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.504</v>
+        <v>0.5084</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4992</v>
+        <v>0.1405</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0048</v>
+        <v>0.3679</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7189</v>
+        <v>-0.6908</v>
       </c>
       <c r="E7" t="n">
         <v>-0.6681</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0508</v>
+        <v>-0.0227</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9469</v>
@@ -1000,13 +1000,13 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0298</v>
+        <v>0.0578</v>
       </c>
       <c r="T7" t="n">
         <v>0.011</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>E. SENZI KITAMBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2048</v>
+        <v>-2.9347</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0969</v>
+        <v>-1.8583</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.108</v>
+        <v>-1.0764</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5538</v>
+        <v>-4.9099</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1885</v>
+        <v>-2.5394</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.3653</v>
+        <v>-2.3705</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4439</v>
+        <v>-2.1345</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6817</v>
+        <v>-0.9409</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2377</v>
+        <v>-1.1937</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.9978</v>
+        <v>-2.7753</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8702</v>
+        <v>-1.5985</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1276</v>
+        <v>-1.1768</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>1.675</v>
+        <v>0.3716</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1749</v>
+        <v>-0.2063</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5002</v>
+        <v>0.578</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0704</v>
+        <v>1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>1.4737</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1962</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. SENZI KITAMBO</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8681</v>
+        <v>-3.1145</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9602</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9079</v>
+        <v>-2.3045</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9099</v>
+        <v>-3.5538</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5394</v>
+        <v>-0.1885</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3705</v>
+        <v>-3.3653</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1345</v>
+        <v>0.4439</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9409</v>
+        <v>1.6817</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1937</v>
+        <v>-1.2377</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7753</v>
+        <v>-3.9978</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5985</v>
+        <v>-1.8702</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1768</v>
+        <v>-2.1276</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4382</v>
+        <v>0.7654</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3082</v>
+        <v>0.4618</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7464</v>
+        <v>0.3036</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2071</v>
+        <v>0.0704</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0168</v>
+        <v>-3.1727</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5108</v>
+        <v>-3.386</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4941</v>
+        <v>0.2133</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4692</v>
@@ -1234,13 +1234,13 @@
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0204</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.132</v>
+        <v>-0.0072</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1525</v>
+        <v>0.8717</v>
       </c>
       <c r="V10" t="n">
         <v>1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6347</v>
+        <v>-4.0679</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5205</v>
+        <v>-1.3749</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1142</v>
+        <v>-2.693</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7146</v>
@@ -1312,13 +1312,13 @@
         <v>2.3787</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3198</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3548</v>
+        <v>0.5004</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.035</v>
+        <v>0.3862</v>
       </c>
       <c r="V11" t="n">
         <v>0.337</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.523300000000001</v>
+        <v>-7.4317</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2884</v>
+        <v>-3.3091</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2349</v>
+        <v>-4.1226</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8268</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7914</v>
+        <v>0.3001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1745</v>
+        <v>-0.1953</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3831</v>
+        <v>0.4954</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.9055</v>
+        <v>-17.2814</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.3003</v>
+        <v>-9.676200000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-7.6052</v>
@@ -1435,7 +1435,7 @@
         <v>-18.1352</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.0907</v>
+        <v>-8.090700000000002</v>
       </c>
       <c r="I13" t="n">
         <v>-10.0444</v>
@@ -1447,7 +1447,7 @@
         <v>4.9267</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1995</v>
+        <v>-0.1995000000000005</v>
       </c>
       <c r="M13" t="n">
         <v>-22.8621</v>
@@ -1468,16 +1468,16 @@
         <v>12.8845</v>
       </c>
       <c r="S13" t="n">
-        <v>3.964500000000001</v>
+        <v>4.588399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.274</v>
+        <v>0.3498999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>4.2386</v>
       </c>
       <c r="V13" t="n">
-        <v>6.176399999999999</v>
+        <v>6.176400000000001</v>
       </c>
       <c r="W13" t="n">
         <v>8.042400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.5258</v>
+        <v>9.4589</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3072</v>
+        <v>8.020300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2186</v>
+        <v>1.4386</v>
       </c>
       <c r="G14" t="n">
         <v>10.8641</v>
@@ -1546,13 +1546,13 @@
         <v>4.1627</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8123</v>
+        <v>-0.8792</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6847</v>
+        <v>-0.9716</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1276</v>
+        <v>0.0925</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7243000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2426</v>
+        <v>3.6967</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3923</v>
+        <v>1.3736</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8503</v>
+        <v>2.3231</v>
       </c>
       <c r="G15" t="n">
         <v>2.5558</v>
@@ -1624,13 +1624,13 @@
         <v>3.9645</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0412</v>
+        <v>-0.5047</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6022999999999999</v>
+        <v>-0.4164</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.0883</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3278</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3112</v>
+        <v>2.8445</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2126</v>
+        <v>1.7745</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5238</v>
+        <v>1.07</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9644</v>
+        <v>1.8935</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.147</v>
+        <v>1.3637</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1115</v>
+        <v>0.5298</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8464</v>
+        <v>2.4507</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0351</v>
+        <v>2.0852</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8113</v>
+        <v>0.3655</v>
       </c>
       <c r="M16" t="n">
-        <v>0.118</v>
+        <v>-0.5572</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1822</v>
+        <v>-0.7215</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3002</v>
+        <v>0.1643</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1893</v>
+        <v>2.7751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1716</v>
+        <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6151</v>
+        <v>-0.8333</v>
       </c>
       <c r="T16" t="n">
-        <v>0.727</v>
+        <v>-0.6762</v>
       </c>
       <c r="U16" t="n">
-        <v>0.888</v>
+        <v>-0.1571</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4577</v>
+        <v>-0.9908</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6539</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2746</v>
+        <v>2.4738</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7164</v>
+        <v>-0.5127</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9911</v>
+        <v>2.9865</v>
       </c>
       <c r="G17" t="n">
         <v>0.7953</v>
@@ -1780,13 +1780,13 @@
         <v>3.9645</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6993</v>
+        <v>-0.5001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0056</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3063</v>
+        <v>0.3017</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7947</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2509</v>
+        <v>1.9686</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2652</v>
+        <v>-1.1294</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9857</v>
+        <v>3.098</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8935</v>
+        <v>0.9644</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3637</v>
+        <v>-0.147</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5298</v>
+        <v>1.1115</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4507</v>
+        <v>0.8464</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0852</v>
+        <v>0.0351</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3655</v>
+        <v>0.8113</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5572</v>
+        <v>0.118</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7215</v>
+        <v>-0.1822</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1643</v>
+        <v>0.3002</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7751</v>
+        <v>1.1893</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7751</v>
+        <v>3.1716</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4269</v>
+        <v>0.2725</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1855</v>
+        <v>-0.1898</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2413</v>
+        <v>0.4623</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9908</v>
+        <v>-0.4577</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9908</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3929</v>
+        <v>0.421</v>
       </c>
       <c r="E20" t="n">
         <v>0.0402</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3528</v>
+        <v>0.3808</v>
       </c>
       <c r="G20" t="n">
         <v>0.176</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1964</v>
+        <v>0.3616</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.2524</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7544</v>
+        <v>0.614</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0844</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7103</v>
+        <v>-0.5451</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2256</v>
+        <v>0.0852</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7929</v>
+        <v>-1.4605</v>
       </c>
       <c r="E22" t="n">
         <v>-1.4303</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3626</v>
+        <v>-0.0302</v>
       </c>
       <c r="G22" t="n">
         <v>1.9797</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3057</v>
+        <v>0.0266</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0696</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2361</v>
+        <v>0.0963</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8811</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7014</v>
+        <v>-2.3853</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6876</v>
+        <v>-1.4838</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0138</v>
+        <v>-0.9015</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2147</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6849</v>
+        <v>-0.3689</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6864</v>
+        <v>-0.4826</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0014</v>
+        <v>0.1138</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>17.9054</v>
+        <v>18.5846</v>
       </c>
       <c r="E24" t="n">
-        <v>7.6053</v>
+        <v>7.605299999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>10.3003</v>
+        <v>10.9793</v>
       </c>
       <c r="G24" t="n">
         <v>18.135</v>
@@ -2299,13 +2299,13 @@
         <v>10.0444</v>
       </c>
       <c r="J24" t="n">
-        <v>22.8621</v>
+        <v>22.86210000000001</v>
       </c>
       <c r="K24" t="n">
         <v>13.0175</v>
       </c>
       <c r="L24" t="n">
-        <v>9.844799999999998</v>
+        <v>9.844799999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-4.7271</v>
@@ -2314,7 +2314,7 @@
         <v>-4.926699999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1996000000000001</v>
+        <v>0.1996</v>
       </c>
       <c r="P24" t="n">
         <v>9.9109</v>
@@ -2326,13 +2326,13 @@
         <v>22.7957</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.9644</v>
+        <v>-3.2854</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.2385</v>
+        <v>-4.238499999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2740000000000001</v>
+        <v>0.9532000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>-6.1764</v>
